--- a/output/Sunset/Cash_Reconciliation_Report.xlsx
+++ b/output/Sunset/Cash_Reconciliation_Report.xlsx
@@ -434,10 +434,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SUNSE DEP Connect X2061:</v>
+        <v>SUNSE PAY Huntington X4310:</v>
       </c>
       <c r="B4" t="str">
-        <v>$73,159.06</v>
+        <v>$109.45</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -445,10 +445,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SUNSE DEP Flagstar X2598:</v>
+        <v>SUNSE GOV Flagstar X2571:</v>
       </c>
       <c r="B5" t="str">
-        <v>$546,884.62</v>
+        <v>$1,470.92</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -456,10 +456,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SUNSE DEP Huntington X8699:</v>
+        <v>SUNSE DEP Connect X2061:</v>
       </c>
       <c r="B6" t="str">
-        <v>$115,970.97</v>
+        <v>$73,159.06</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -467,10 +467,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SUNSE GOV Connect X3971:</v>
+        <v>SUNSE OPE Connect X9733:</v>
       </c>
       <c r="B7" t="str">
-        <v>$95,073.05</v>
+        <v>$84,000.00</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -478,10 +478,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SUNSE GOV Flagstar X2571:</v>
+        <v>SUNSE OPE Connect X3128:</v>
       </c>
       <c r="B8" t="str">
-        <v>$1,470.92</v>
+        <v>$94,773.05</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -489,10 +489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SUNSE GOV Huntington X8686:</v>
+        <v>SUNSE GOV Connect X3971:</v>
       </c>
       <c r="B9" t="str">
-        <v>$610,313.04</v>
+        <v>$95,073.05</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -500,10 +500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SUNSE OPE Connect X3128:</v>
+        <v>SUNSE DEP Huntington X8699:</v>
       </c>
       <c r="B10" t="str">
-        <v>$94,773.05</v>
+        <v>$115,970.97</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -511,10 +511,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SUNSE OPE Connect X9733:</v>
+        <v>SUNSE PAY Flagstar X2563:</v>
       </c>
       <c r="B11" t="str">
-        <v>$84,000.00</v>
+        <v>$482,121.63</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -522,10 +522,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SUNSE OPE Flagstar X2555:</v>
+        <v>SUNSE DEP Flagstar X2598:</v>
       </c>
       <c r="B12" t="str">
-        <v>$1,377,052.25</v>
+        <v>$546,884.62</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -533,10 +533,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SUNSE OPE Huntington X8709:</v>
+        <v>SUNSE GOV Huntington X8686:</v>
       </c>
       <c r="B13" t="str">
-        <v>$780,635.31</v>
+        <v>$610,313.04</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -544,10 +544,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SUNSE PAY Flagstar X2563:</v>
+        <v>SUNSE OPE Huntington X8709:</v>
       </c>
       <c r="B14" t="str">
-        <v>$482,121.63</v>
+        <v>$780,635.31</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -555,10 +555,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SUNSE PAY Huntington X4310:</v>
+        <v>SUNSE OPE Flagstar X2555:</v>
       </c>
       <c r="B15" t="str">
-        <v>$109.45</v>
+        <v>$1,377,052.25</v>
       </c>
       <c r="C15" t="str">
         <v/>
